--- a/Excel/ROMAN-NEW.xlsx
+++ b/Excel/ROMAN-NEW.xlsx
@@ -5,28 +5,22 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NGODING\BOOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NGODING\BOOS\BOOS\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C68A1574-E674-4B2F-B3CC-925E4D5CEBA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B8873A-A9D3-48FA-8F20-49CC4F3D9184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{2365EE53-A184-4A0D-8F8A-B3FA5A6F3E66}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2365EE53-A184-4A0D-8F8A-B3FA5A6F3E66}"/>
   </bookViews>
   <sheets>
-    <sheet name="5664-SYDIB-RO-259955" sheetId="1" r:id="rId1"/>
+    <sheet name="FORM" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
-  <si>
-    <t>STORE ORDER NO</t>
-  </si>
-  <si>
-    <t>STORE CUSTOMER</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>BLIND TYPE</t>
   </si>
@@ -67,9 +61,6 @@
     <t>Right</t>
   </si>
   <si>
-    <t>Facade</t>
-  </si>
-  <si>
     <t>DESIGN TYPE</t>
   </si>
   <si>
@@ -103,9 +94,6 @@
     <t>Coffee</t>
   </si>
   <si>
-    <t>Test</t>
-  </si>
-  <si>
     <t>CONTROL LENGTH</t>
   </si>
   <si>
@@ -118,13 +106,28 @@
     <t>NEO BOX</t>
   </si>
   <si>
-    <t>Altus</t>
-  </si>
-  <si>
-    <t>No Remote</t>
-  </si>
-  <si>
-    <t>Retrousse</t>
+    <t>ORDER NUMBER</t>
+  </si>
+  <si>
+    <t>ORDER NAME</t>
+  </si>
+  <si>
+    <t>ORDER NOTE</t>
+  </si>
+  <si>
+    <t>Your Order Number</t>
+  </si>
+  <si>
+    <t>Your Order Name</t>
+  </si>
+  <si>
+    <t>Your Order Note</t>
+  </si>
+  <si>
+    <t>Room 1</t>
+  </si>
+  <si>
+    <t>No Cover Valance</t>
   </si>
 </sst>
 </file>
@@ -267,7 +270,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -445,6 +448,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -608,8 +617,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -965,132 +975,138 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAA9DE9D-E6D2-4792-92D2-8E2EE66F004B}">
-  <dimension ref="A1:T5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:T4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="26.7109375" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.28515625" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" customWidth="1"/>
-    <col min="12" max="12" width="18.140625" customWidth="1"/>
-    <col min="13" max="13" width="20.42578125" customWidth="1"/>
-    <col min="14" max="14" width="31.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="19.140625" customWidth="1"/>
-    <col min="19" max="19" width="17.85546875" customWidth="1"/>
-    <col min="20" max="20" width="24.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="26.6640625" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.33203125" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" customWidth="1"/>
+    <col min="12" max="12" width="18.109375" customWidth="1"/>
+    <col min="13" max="13" width="20.44140625" customWidth="1"/>
+    <col min="14" max="14" width="31.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="19.109375" customWidth="1"/>
+    <col min="19" max="19" width="17.88671875" customWidth="1"/>
+    <col min="20" max="20" width="24.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
         <v>1</v>
       </c>
+      <c r="H3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M3" t="s">
+        <v>7</v>
+      </c>
+      <c r="N3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P3" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R3" t="s">
+        <v>27</v>
+      </c>
+      <c r="S3" t="s">
+        <v>2</v>
+      </c>
+      <c r="T3" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>131313</v>
-      </c>
-      <c r="B2">
-        <v>131313</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
         <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M3" t="s">
-        <v>9</v>
-      </c>
-      <c r="N3" t="s">
-        <v>22</v>
-      </c>
-      <c r="O3" t="s">
-        <v>28</v>
-      </c>
-      <c r="P3" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>30</v>
-      </c>
-      <c r="R3" t="s">
-        <v>31</v>
-      </c>
-      <c r="S3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J4">
         <v>1000</v>
@@ -1099,57 +1115,13 @@
         <v>1000</v>
       </c>
       <c r="L4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5">
-        <v>1000</v>
-      </c>
-      <c r="K5">
-        <v>1000</v>
-      </c>
-      <c r="L5" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N5" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/ROMAN-NEW.xlsx
+++ b/Excel/ROMAN-NEW.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NGODING\BOOS\BOOS\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B8873A-A9D3-48FA-8F20-49CC4F3D9184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0D374C-045B-4E2F-B2E9-F2864CA8DEBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2365EE53-A184-4A0D-8F8A-B3FA5A6F3E66}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
   <si>
     <t>BLIND TYPE</t>
   </si>
@@ -128,6 +128,21 @@
   </si>
   <si>
     <t>No Cover Valance</t>
+  </si>
+  <si>
+    <t>Plantation</t>
+  </si>
+  <si>
+    <t>Altus</t>
+  </si>
+  <si>
+    <t>Room 2</t>
+  </si>
+  <si>
+    <t>Cover Valance</t>
+  </si>
+  <si>
+    <t>Left</t>
   </si>
 </sst>
 </file>
@@ -975,7 +990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAA9DE9D-E6D2-4792-92D2-8E2EE66F004B}">
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
@@ -1124,6 +1139,50 @@
         <v>21</v>
       </c>
     </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5">
+        <v>1000</v>
+      </c>
+      <c r="K5">
+        <v>1000</v>
+      </c>
+      <c r="L5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N5" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Excel/ROMAN-NEW.xlsx
+++ b/Excel/ROMAN-NEW.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NGODING\BOOS\BOOS\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0D374C-045B-4E2F-B2E9-F2864CA8DEBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{458A0BE1-FA19-4D09-B7DA-88B0AD86804B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2365EE53-A184-4A0D-8F8A-B3FA5A6F3E66}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
   <si>
     <t>BLIND TYPE</t>
   </si>
@@ -130,9 +130,6 @@
     <t>No Cover Valance</t>
   </si>
   <si>
-    <t>Plantation</t>
-  </si>
-  <si>
     <t>Altus</t>
   </si>
   <si>
@@ -143,6 +140,12 @@
   </si>
   <si>
     <t>Left</t>
+  </si>
+  <si>
+    <t>Telis 1 RTS (Pure)</t>
+  </si>
+  <si>
+    <t>Reg Cord Lock</t>
   </si>
 </sst>
 </file>
@@ -990,7 +993,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAA9DE9D-E6D2-4792-92D2-8E2EE66F004B}">
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
@@ -1147,16 +1150,16 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
         <v>36</v>
-      </c>
-      <c r="D5" t="s">
-        <v>37</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G5" t="s">
         <v>10</v>
@@ -1174,13 +1177,54 @@
         <v>1000</v>
       </c>
       <c r="L5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" t="s">
         <v>39</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>40</v>
       </c>
-      <c r="N5" t="s">
-        <v>21</v>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6">
+        <v>1000</v>
+      </c>
+      <c r="K6">
+        <v>1000</v>
+      </c>
+      <c r="L6" t="s">
+        <v>38</v>
+      </c>
+      <c r="M6" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
